--- a/artfynd/A 51232-2023 artfynd.xlsx
+++ b/artfynd/A 51232-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51232-2023 artfynd.xlsx
+++ b/artfynd/A 51232-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113888568</v>
+        <v>1942573</v>
       </c>
       <c r="B2" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,24 +703,20 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rullbo, Dlr</t>
+          <t>Hamra kronopark, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493258</v>
+        <v>493324</v>
       </c>
       <c r="R2" t="n">
-        <v>6844810</v>
+        <v>6844704</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2009-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2009-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,18 +757,231 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Via Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113888568</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rullbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>493258</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6844810</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6553625</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hamra kronopark, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>493324</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6844704</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2009-08-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2009-08-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51232-2023 artfynd.xlsx
+++ b/artfynd/A 51232-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1942573</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888568</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,8 +997,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6553625</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>